--- a/Web/TestCases/Soporte.xlsx
+++ b/Web/TestCases/Soporte.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{315BAAC4-FAC1-48EC-9094-D7A719A049F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5198EE8-01BC-4206-B0D1-997B5E50181E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="315" yWindow="5190" windowWidth="28020" windowHeight="8700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
   <si>
     <t>Num</t>
   </si>
@@ -70,9 +70,6 @@
     <t>SOP004</t>
   </si>
   <si>
-    <t>New request for support</t>
-  </si>
-  <si>
     <t>New request for support: cancel</t>
   </si>
   <si>
@@ -86,6 +83,36 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1kEUaI7F-yU1VSXMaZwqlgMynkst4qhQV/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Soporte"</t>
+  </si>
+  <si>
+    <t>1.The user  clicks "Nueva petición"
+2. Fills the mandatory fields
+2. Clicks "Crear petición"</t>
+  </si>
+  <si>
+    <t>New request for support (mandatory fields)</t>
+  </si>
+  <si>
+    <t>New request for support (all fields)</t>
+  </si>
+  <si>
+    <t>1.The user  clicks "Nueva petición"
+2. Fills all fields
+2. Clicks "Crear petición"</t>
+  </si>
+  <si>
+    <t>SOP005</t>
+  </si>
+  <si>
+    <t>BL</t>
+  </si>
+  <si>
+    <t>1.The user  clicks "Nueva petición"
+2. Fills all fields
+2. Clicks "Cancelar"</t>
   </si>
 </sst>
 </file>
@@ -529,7 +556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -575,17 +602,21 @@
       <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="3"/>
+      <c r="D2" s="3" t="s">
+        <v>21</v>
+      </c>
       <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G2" s="8" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -593,21 +624,23 @@
         <v>13</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="E3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -615,37 +648,67 @@
         <v>14</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="E4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="3"/>
-      <c r="G4" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="4"/>
     </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+      <c r="C5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>19</v>
+      </c>
       <c r="G5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="4"/>
+      <c r="H6" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G5">
+  <conditionalFormatting sqref="G2:G6">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
